--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Traffico.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Traffico.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="119">
   <si>
     <r>
       <t xml:space="preserve">
@@ -500,7 +500,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> subirà queste variazioni: 
+      <t xml:space="preserve"> subirà queste variazioni:
 </t>
     </r>
     <r>
@@ -580,7 +580,7 @@
         <sz val="10"/>
         <rFont val="Titillium Web"/>
       </rPr>
-      <t xml:space="preserve"> subirà queste variazioni:  
+      <t xml:space="preserve"> subirà queste variazioni:
 </t>
     </r>
     <r>
@@ -992,7 +992,7 @@
       <rPr>
         <b/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr/>
@@ -1078,14 +1078,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Promemoria automatici — Messaggi Premium
-Impostando il messaggio di Avviso di pagamento come Messaggio Premium, disponibile a seconda della tipologia di contratto sottoscritto dall’ente, non è necessario inviare il seguente messaggio di promemoria.
-Gli utenti che hanno dato il loro consenso, infatti, riceveranno automaticamente una notifica push sui loro dispositivi all’avvicinarsi della scadenza.</t>
   </si>
   <si>
     <t xml:space="preserve">Mancato pagamento
@@ -2028,16 +2020,16 @@
         <v>60</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="H11" s="34" t="s">
         <v>60</v>
       </c>
       <c r="I11" s="34" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="J11" s="34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K11" s="34" t="s">
         <v>60</v>
